--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CBI ELCHE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CBI ELCHE.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>67.5889</v>
+        <v>51.9203</v>
       </c>
       <c r="E2" t="n">
-        <v>56.7908</v>
+        <v>43.7429</v>
       </c>
       <c r="F2" t="n">
-        <v>10.7984</v>
+        <v>8.177099999999999</v>
       </c>
       <c r="G2" t="n">
         <v>4.8706</v>
@@ -610,13 +610,13 @@
         <v>50.949</v>
       </c>
       <c r="S2" t="n">
-        <v>33.9258</v>
+        <v>18.2572</v>
       </c>
       <c r="T2" t="n">
-        <v>26.0917</v>
+        <v>13.044</v>
       </c>
       <c r="U2" t="n">
-        <v>7.8338</v>
+        <v>5.2131</v>
       </c>
       <c r="V2" t="n">
         <v>11.6209</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>M. VARELA BARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>40.0963</v>
+        <v>42.7336</v>
       </c>
       <c r="E3" t="n">
-        <v>37.1583</v>
+        <v>41.7578</v>
       </c>
       <c r="F3" t="n">
-        <v>2.938099999999999</v>
+        <v>0.9754000000000007</v>
       </c>
       <c r="G3" t="n">
-        <v>18.9011</v>
+        <v>26.5315</v>
       </c>
       <c r="H3" t="n">
-        <v>20.2183</v>
+        <v>1.841099999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.317</v>
+        <v>24.6905</v>
       </c>
       <c r="J3" t="n">
-        <v>39.3483</v>
+        <v>54.4827</v>
       </c>
       <c r="K3" t="n">
-        <v>32.2059</v>
+        <v>23.3904</v>
       </c>
       <c r="L3" t="n">
-        <v>7.1426</v>
+        <v>31.092</v>
       </c>
       <c r="M3" t="n">
-        <v>-20.4468</v>
+        <v>-27.9511</v>
       </c>
       <c r="N3" t="n">
-        <v>-11.9875</v>
+        <v>-21.5491</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.4594</v>
+        <v>-6.402100000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>5.472300000000001</v>
+        <v>-5.0949</v>
       </c>
       <c r="Q3" t="n">
-        <v>-24.7197</v>
+        <v>-45.8541</v>
       </c>
       <c r="R3" t="n">
-        <v>30.192</v>
+        <v>40.7592</v>
       </c>
       <c r="S3" t="n">
-        <v>29.2893</v>
+        <v>4.1283</v>
       </c>
       <c r="T3" t="n">
-        <v>25.1549</v>
+        <v>5.5282</v>
       </c>
       <c r="U3" t="n">
-        <v>4.1344</v>
+        <v>-1.3997</v>
       </c>
       <c r="V3" t="n">
-        <v>-13.5667</v>
+        <v>17.1687</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.6254</v>
+        <v>27.6012</v>
       </c>
       <c r="X3" t="n">
-        <v>-10.9413</v>
+        <v>-10.4327</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. VARELA BARCIA</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>30.0894</v>
+        <v>24.2971</v>
       </c>
       <c r="E4" t="n">
-        <v>33.0225</v>
+        <v>23.2872</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.932899999999999</v>
+        <v>1.009699999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>26.5315</v>
+        <v>18.9011</v>
       </c>
       <c r="H4" t="n">
-        <v>1.841099999999999</v>
+        <v>20.2183</v>
       </c>
       <c r="I4" t="n">
-        <v>24.6905</v>
+        <v>-1.317</v>
       </c>
       <c r="J4" t="n">
-        <v>54.4827</v>
+        <v>39.3483</v>
       </c>
       <c r="K4" t="n">
-        <v>23.3904</v>
+        <v>32.2059</v>
       </c>
       <c r="L4" t="n">
-        <v>31.092</v>
+        <v>7.1426</v>
       </c>
       <c r="M4" t="n">
-        <v>-27.9511</v>
+        <v>-20.4468</v>
       </c>
       <c r="N4" t="n">
-        <v>-21.5491</v>
+        <v>-11.9875</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.402100000000001</v>
+        <v>-8.4594</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.0949</v>
+        <v>5.472300000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-45.8541</v>
+        <v>-24.7197</v>
       </c>
       <c r="R4" t="n">
-        <v>40.7592</v>
+        <v>30.192</v>
       </c>
       <c r="S4" t="n">
-        <v>-8.515500000000001</v>
+        <v>13.4899</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.2074</v>
+        <v>11.2841</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.3083</v>
+        <v>2.2061</v>
       </c>
       <c r="V4" t="n">
-        <v>17.1687</v>
+        <v>-13.5667</v>
       </c>
       <c r="W4" t="n">
-        <v>27.6012</v>
+        <v>-2.6254</v>
       </c>
       <c r="X4" t="n">
-        <v>-10.4327</v>
+        <v>-10.9413</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>27.5097</v>
+        <v>16.3971</v>
       </c>
       <c r="E5" t="n">
-        <v>21.4088</v>
+        <v>11.9409</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1012</v>
+        <v>4.456300000000001</v>
       </c>
       <c r="G5" t="n">
         <v>1.9271</v>
@@ -844,13 +844,13 @@
         <v>18.4926</v>
       </c>
       <c r="S5" t="n">
-        <v>21.2804</v>
+        <v>10.1677</v>
       </c>
       <c r="T5" t="n">
-        <v>16.2918</v>
+        <v>6.8241</v>
       </c>
       <c r="U5" t="n">
-        <v>4.9887</v>
+        <v>3.3438</v>
       </c>
       <c r="V5" t="n">
         <v>-1.9248</v>
@@ -877,13 +877,13 @@
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>15.8212</v>
+        <v>11.4456</v>
       </c>
       <c r="E6" t="n">
-        <v>10.1258</v>
+        <v>6.952300000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>5.6957</v>
+        <v>4.4933</v>
       </c>
       <c r="G6" t="n">
         <v>4.385</v>
@@ -922,13 +922,13 @@
         <v>17.3604</v>
       </c>
       <c r="S6" t="n">
-        <v>9.069900000000001</v>
+        <v>4.6943</v>
       </c>
       <c r="T6" t="n">
-        <v>5.7255</v>
+        <v>2.552</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3443</v>
+        <v>2.1421</v>
       </c>
       <c r="V6" t="n">
         <v>-0.08650000000000002</v>
@@ -955,13 +955,13 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>6.546799999999999</v>
+        <v>9.226000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.012699999999999</v>
+        <v>0.4834999999999996</v>
       </c>
       <c r="F7" t="n">
-        <v>8.5596</v>
+        <v>8.7424</v>
       </c>
       <c r="G7" t="n">
         <v>13.0188</v>
@@ -1000,13 +1000,13 @@
         <v>15.096</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6602000000000001</v>
+        <v>3.3393</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.1426</v>
+        <v>0.3538</v>
       </c>
       <c r="U7" t="n">
-        <v>2.8027</v>
+        <v>2.9853</v>
       </c>
       <c r="V7" t="n">
         <v>-6.0001</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. MALONE NAVARRO</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>4.884399999999999</v>
+        <v>8.391999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>5.2535</v>
+        <v>11.3263</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3690999999999994</v>
+        <v>-2.9342</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0656</v>
+        <v>-0.8480000000000003</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.4129</v>
+        <v>6.653</v>
       </c>
       <c r="I8" t="n">
-        <v>6.3475</v>
+        <v>-7.500999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>10.7753</v>
+        <v>24.2469</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3351</v>
+        <v>23.9385</v>
       </c>
       <c r="L8" t="n">
-        <v>9.440099999999999</v>
+        <v>0.3087000000000006</v>
       </c>
       <c r="M8" t="n">
-        <v>-12.8405</v>
+        <v>-25.0949</v>
       </c>
       <c r="N8" t="n">
-        <v>-9.747999999999999</v>
+        <v>-17.2855</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.0929</v>
+        <v>-7.809399999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7547999999999999</v>
+        <v>7.9254</v>
       </c>
       <c r="Q8" t="n">
-        <v>-16.0395</v>
+        <v>-29.4372</v>
       </c>
       <c r="R8" t="n">
-        <v>16.7943</v>
+        <v>37.3626</v>
       </c>
       <c r="S8" t="n">
-        <v>6.4433</v>
+        <v>5.0039</v>
       </c>
       <c r="T8" t="n">
-        <v>4.0089</v>
+        <v>1.631</v>
       </c>
       <c r="U8" t="n">
-        <v>2.434</v>
+        <v>3.373</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2482</v>
+        <v>-3.6891</v>
       </c>
       <c r="W8" t="n">
-        <v>6.508800000000001</v>
+        <v>14.8854</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.757000000000001</v>
+        <v>-18.5745</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. MEJIA ACOSTA</t>
+          <t>B. MALONE NAVARRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>3.526200000000001</v>
+        <v>5.493199999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0337</v>
+        <v>4.3396</v>
       </c>
       <c r="F9" t="n">
-        <v>4.559799999999999</v>
+        <v>1.1535</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.462800000000001</v>
+        <v>-2.0656</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8783</v>
+        <v>-8.4129</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.3413</v>
+        <v>6.3475</v>
       </c>
       <c r="J9" t="n">
-        <v>12.173</v>
+        <v>10.7753</v>
       </c>
       <c r="K9" t="n">
-        <v>16.1056</v>
+        <v>1.3351</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.9326</v>
+        <v>9.440099999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.6358</v>
+        <v>-12.8405</v>
       </c>
       <c r="N9" t="n">
-        <v>-13.2273</v>
+        <v>-9.747999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4087000000000001</v>
+        <v>-3.0929</v>
       </c>
       <c r="P9" t="n">
-        <v>-9.435</v>
+        <v>0.7547999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-28.8711</v>
+        <v>-16.0395</v>
       </c>
       <c r="R9" t="n">
-        <v>19.4361</v>
+        <v>16.7943</v>
       </c>
       <c r="S9" t="n">
-        <v>12.0692</v>
+        <v>7.0521</v>
       </c>
       <c r="T9" t="n">
-        <v>6.7031</v>
+        <v>3.0951</v>
       </c>
       <c r="U9" t="n">
-        <v>5.366</v>
+        <v>3.9568</v>
       </c>
       <c r="V9" t="n">
-        <v>2.3549</v>
+        <v>-0.2482</v>
       </c>
       <c r="W9" t="n">
-        <v>8.9612</v>
+        <v>6.508800000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.6063</v>
+        <v>-6.757000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. MEJÍA ACOSTA</t>
+          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>2.1849</v>
+        <v>3.051399999999998</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1849</v>
+        <v>11.396</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-8.3447</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1849</v>
+        <v>-1.808499999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9510000000000001</v>
+        <v>-10.8115</v>
       </c>
       <c r="I10" t="n">
-        <v>1.234</v>
+        <v>9.0023</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1849</v>
+        <v>31.245</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9510000000000001</v>
+        <v>9.0877</v>
       </c>
       <c r="L10" t="n">
-        <v>1.234</v>
+        <v>22.1572</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-33.054</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-19.8994</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-13.1548</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.5853</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-39.2496</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>42.8349</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.516</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.1002</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.4157</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.2409999999999997</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>18.3002</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-18.5413</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. MÖLLERMARK</t>
+          <t>G. MEJÍA ACOSTA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,34 +1264,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9339</v>
+        <v>2.1849</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9339</v>
+        <v>2.1849</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9339</v>
+        <v>2.1849</v>
       </c>
       <c r="H11" t="n">
-        <v>0.317</v>
+        <v>0.9510000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.617</v>
+        <v>1.234</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9339</v>
+        <v>2.1849</v>
       </c>
       <c r="K11" t="n">
-        <v>0.317</v>
+        <v>0.9510000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.617</v>
+        <v>1.234</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1207999999999999</v>
+        <v>1.374</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7739</v>
+        <v>-1.2279</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8945</v>
+        <v>2.6019</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9382</v>
@@ -1390,13 +1390,13 @@
         <v>4.340100000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.639</v>
+        <v>0.6141</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8732</v>
+        <v>-0.3272</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2342</v>
+        <v>0.9414</v>
       </c>
       <c r="V12" t="n">
         <v>3.4528</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>R. MÖLLERMARK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2342</v>
+        <v>0.9339</v>
       </c>
       <c r="E13" t="n">
-        <v>5.006499999999999</v>
+        <v>0.9339</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.241099999999999</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8480000000000003</v>
+        <v>0.9339</v>
       </c>
       <c r="H13" t="n">
-        <v>6.653</v>
+        <v>0.317</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.500999999999999</v>
+        <v>0.617</v>
       </c>
       <c r="J13" t="n">
-        <v>24.2469</v>
+        <v>0.9339</v>
       </c>
       <c r="K13" t="n">
-        <v>23.9385</v>
+        <v>0.317</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3087000000000006</v>
+        <v>0.617</v>
       </c>
       <c r="M13" t="n">
-        <v>-25.0949</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-17.2855</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.809399999999999</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>7.9254</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-29.4372</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>37.3626</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.6224</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.6887</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0662</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.6891</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>14.8854</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.5745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. CIPITELLI MONJES</t>
+          <t>A. DIEZ RUANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8103</v>
+        <v>-0.4459000000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1764</v>
+        <v>-0.9938</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6339</v>
+        <v>0.5478999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3741</v>
+        <v>-0.009000000000000091</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.504</v>
+        <v>0.493</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1299</v>
+        <v>-0.5021</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.3983</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.169</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0.5673</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3741</v>
+        <v>0.3890999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.504</v>
+        <v>0.3239</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1299</v>
+        <v>0.06520000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4362</v>
+        <v>-0.5692</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1764</v>
+        <v>-0.5958</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2598</v>
+        <v>0.02660000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DIEZ RUANO</t>
+          <t>M. CIPITELLI MONJES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9726000000000001</v>
+        <v>-0.7128</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1501</v>
+        <v>-0.0789</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1776</v>
+        <v>-0.6339</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.009000000000000091</v>
+        <v>-0.3741</v>
       </c>
       <c r="H15" t="n">
-        <v>0.493</v>
+        <v>-0.504</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5021</v>
+        <v>0.1299</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3983</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.169</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5673</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3890999999999999</v>
+        <v>-0.3741</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3239</v>
+        <v>-0.504</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06520000000000001</v>
+        <v>0.1299</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0958</v>
+        <v>-0.3388</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.752</v>
+        <v>-0.0789</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3439</v>
+        <v>-0.2598</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. MOLLERMARK</t>
+          <t>G. MEJIA ACOSTA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.8668</v>
+        <v>-1.5218</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2472000000000003</v>
+        <v>-3.953399999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.114</v>
+        <v>2.431699999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5425</v>
+        <v>-1.462800000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5729000000000001</v>
+        <v>2.8783</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9696</v>
+        <v>-4.3413</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5802</v>
+        <v>12.173</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9658</v>
+        <v>16.1056</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3857</v>
+        <v>-3.9326</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.1226</v>
+        <v>-13.6358</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.5387</v>
+        <v>-13.2273</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5838000000000001</v>
+        <v>-0.4087000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5661</v>
+        <v>-9.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0192</v>
+        <v>-28.8711</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4531</v>
+        <v>19.4361</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.381</v>
+        <v>7.0212</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4835</v>
+        <v>3.7834</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8976</v>
+        <v>3.238</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6226</v>
+        <v>2.3549</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1696</v>
+        <v>8.9612</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.547</v>
+        <v>-6.6063</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CABALLERO ROMERO</t>
+          <t>R. MOLLERMARK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.5955</v>
+        <v>-1.8365</v>
       </c>
       <c r="E17" t="n">
-        <v>2.671</v>
+        <v>0.4621000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.2667</v>
+        <v>-2.2986</v>
       </c>
       <c r="G17" t="n">
-        <v>-8.516500000000001</v>
+        <v>-1.5425</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.8314</v>
+        <v>-0.5729000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.6848</v>
+        <v>-0.9696</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3220999999999998</v>
+        <v>1.5802</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0519</v>
+        <v>1.9658</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.3739</v>
+        <v>-0.3857</v>
       </c>
       <c r="M17" t="n">
-        <v>-8.1942</v>
+        <v>-3.1226</v>
       </c>
       <c r="N17" t="n">
-        <v>-4.8835</v>
+        <v>-2.5387</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.3112</v>
+        <v>-0.5838000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0757</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6.4158</v>
+        <v>-3.0192</v>
       </c>
       <c r="R17" t="n">
-        <v>8.4915</v>
+        <v>2.4531</v>
       </c>
       <c r="S17" t="n">
-        <v>4.4068</v>
+        <v>-0.3506</v>
       </c>
       <c r="T17" t="n">
-        <v>6.3148</v>
+        <v>-0.2685</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.9079</v>
+        <v>-0.08209999999999991</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5618</v>
+        <v>0.6226</v>
       </c>
       <c r="W17" t="n">
-        <v>3.094</v>
+        <v>2.1696</v>
       </c>
       <c r="X17" t="n">
-        <v>-4.6558</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.350899999999999</v>
+        <v>-3.1818</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5618</v>
+        <v>-0.7822000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7893</v>
+        <v>-2.3995</v>
       </c>
       <c r="G18" t="n">
         <v>-4.5532</v>
@@ -1858,13 +1858,13 @@
         <v>1.3209</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7794000000000001</v>
+        <v>0.3897999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8078000000000001</v>
+        <v>-0.02829999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.02829999999999999</v>
+        <v>0.4182</v>
       </c>
       <c r="V18" t="n">
         <v>0.03799999999999991</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
+          <t>A. CABALLERO ROMERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>-15.241</v>
+        <v>-4.8824</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.795700000000002</v>
+        <v>-0.1144000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-12.4455</v>
+        <v>-4.768000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.808499999999999</v>
+        <v>-8.516500000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-10.8115</v>
+        <v>-2.8314</v>
       </c>
       <c r="I19" t="n">
-        <v>9.0023</v>
+        <v>-5.6848</v>
       </c>
       <c r="J19" t="n">
-        <v>31.245</v>
+        <v>-0.3220999999999998</v>
       </c>
       <c r="K19" t="n">
-        <v>9.0877</v>
+        <v>2.0519</v>
       </c>
       <c r="L19" t="n">
-        <v>22.1572</v>
+        <v>-2.3739</v>
       </c>
       <c r="M19" t="n">
-        <v>-33.054</v>
+        <v>-8.1942</v>
       </c>
       <c r="N19" t="n">
-        <v>-19.8994</v>
+        <v>-4.8835</v>
       </c>
       <c r="O19" t="n">
-        <v>-13.1548</v>
+        <v>-3.3112</v>
       </c>
       <c r="P19" t="n">
-        <v>3.5853</v>
+        <v>2.0757</v>
       </c>
       <c r="Q19" t="n">
-        <v>-39.2496</v>
+        <v>-6.4158</v>
       </c>
       <c r="R19" t="n">
-        <v>42.8349</v>
+        <v>8.4915</v>
       </c>
       <c r="S19" t="n">
-        <v>-16.7766</v>
+        <v>3.1202</v>
       </c>
       <c r="T19" t="n">
-        <v>-13.0917</v>
+        <v>3.5296</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.6851</v>
+        <v>-0.4095</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2409999999999997</v>
+        <v>-1.5618</v>
       </c>
       <c r="W19" t="n">
-        <v>18.3002</v>
+        <v>3.094</v>
       </c>
       <c r="X19" t="n">
-        <v>-18.5413</v>
+        <v>-4.6558</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>-32.7453</v>
+        <v>-10.5815</v>
       </c>
       <c r="E20" t="n">
-        <v>-16.2177</v>
+        <v>-1.461199999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-16.5273</v>
+        <v>-9.1197</v>
       </c>
       <c r="G20" t="n">
         <v>-19.3628</v>
@@ -2014,13 +2014,13 @@
         <v>45.8541</v>
       </c>
       <c r="S20" t="n">
-        <v>-22.3814</v>
+        <v>-0.2176000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-14.6563</v>
+        <v>0.09980000000000022</v>
       </c>
       <c r="U20" t="n">
-        <v>-7.725</v>
+        <v>-0.3173</v>
       </c>
       <c r="V20" t="n">
         <v>-4.775700000000001</v>
@@ -2047,13 +2047,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>-35.3045</v>
+        <v>-27.7635</v>
       </c>
       <c r="E21" t="n">
-        <v>-24.3753</v>
+        <v>-16.789</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.929</v>
+        <v>-10.9741</v>
       </c>
       <c r="G21" t="n">
         <v>-17.1011</v>
@@ -2092,13 +2092,13 @@
         <v>28.6824</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.0426</v>
+        <v>4.4982</v>
       </c>
       <c r="T21" t="n">
-        <v>-8.5205</v>
+        <v>-0.9342999999999998</v>
       </c>
       <c r="U21" t="n">
-        <v>5.478</v>
+        <v>5.432700000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-18.1799</v>
@@ -2125,22 +2125,22 @@
         <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>103.1814</v>
+        <v>126.5229</v>
       </c>
       <c r="E22" t="n">
-        <v>123.7059</v>
+        <v>133.4066</v>
       </c>
       <c r="F22" t="n">
-        <v>-20.5239</v>
+        <v>-6.8835</v>
       </c>
       <c r="G22" t="n">
-        <v>13.1706</v>
+        <v>13.17059999999999</v>
       </c>
       <c r="H22" t="n">
         <v>21.9516</v>
       </c>
       <c r="I22" t="n">
-        <v>-8.7811</v>
+        <v>-8.781100000000006</v>
       </c>
       <c r="J22" t="n">
         <v>278.0775</v>
@@ -2158,7 +2158,7 @@
         <v>-177.2934</v>
       </c>
       <c r="O22" t="n">
-        <v>-87.61499999999999</v>
+        <v>-87.61500000000001</v>
       </c>
       <c r="P22" t="n">
         <v>47.175</v>
@@ -2170,13 +2170,13 @@
         <v>381.174</v>
       </c>
       <c r="S22" t="n">
-        <v>58.47500000000002</v>
+        <v>81.816</v>
       </c>
       <c r="T22" t="n">
-        <v>40.89059999999999</v>
+        <v>50.5923</v>
       </c>
       <c r="U22" t="n">
-        <v>17.58300000000001</v>
+        <v>31.2244</v>
       </c>
       <c r="V22" t="n">
         <v>-15.6385</v>
